--- a/04_DESIGN_TABLES/DesignTable_2408.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2408.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -451,8 +451,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:V18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -577,6 +577,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1376,10 +1381,10 @@
         <v>1.31</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1.125</v>
+        <v>1.25</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1.25</v>
+        <v>1.1875</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0.125</v>
@@ -1420,22 +1425,22 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>VERIFIED</t>
+          <t>[BRENNAN-CELL 2026-10-20: HEXB@HEX] JIC end: MS33656J==Brennan fleet; L3 1.31: Air-Way == Brennan TFA p66 "L LGTH" 1.310; THDMAJ_B@DRIVE 1.1875 = JIC -14 thread major (gen_straight2 JIC[14] = 2403 table, = the row's own EndB_Thread 1 3/16-12): repairs the 2026-09 column shift (the cell held the voted hex 1.25); HEXB@HEX: Brennan TFA catalog p.66 table TFA-p066-t05 "MJ PLUG" row 2408-14 col "C HEX" = 1.250 (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_index.json, page verified True) [user 2026-10-20 Q1: Air-Way value cannot be built -&gt; Brennan ("use brennans")] (Air-Way printed 1.125: the hex (1.125 across the flats) is smaller than its own 1 3/16-12 JIC thread (major 1.1875); MS51518D prints 1 1/4 (this row's 2026-09 $COMMENT))</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>CONFLICT vs MS51518 hex: AW 1.125 vs MS 1 1/4 | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size)</t>
+          <t>CONFLICT vs MS51518 hex: AW 1.125 vs MS 1 1/4 | BUILD (OMi SKU does not state solid/hollow - matched to every plug variant of this size) | 2026-10-20 HEXB@HEX = Brennan 1.25 (Air-Way 1.125 cannot be built: the hex (1.125 across the flats) is smaller than its own 1 3/16-12 JIC thread (major 1.1875); MS51518D prints 1 1/4 (this row's 2026-09 $COMMENT))</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>RESOLVED 2-1: hex=1.250 (MS51518+Brennan drawing agree; Air-Way printed 1.125, outvoted)</t>
+          <t>SUPERSEDED 2026-10-20: hex 1.250 by the user Q1 rule (Air-Way 1.125 not buildable -&gt; Brennan), not by a vote | was: RESOLVED 2-1: hex=1.250 (MS51518+Brennan drawing agree; Air-Way printed 1.125, outvoted)</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1446,6 +1451,11 @@
       <c r="U13" t="inlineStr">
         <is>
           <t>2408-14</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
